--- a/exports/PETRONET_full_report.xlsx
+++ b/exports/PETRONET_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.65</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.38541666666</v>
+        <v>44580.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>201.4</v>
+        <v>201.1</v>
       </c>
       <c r="I2" t="n">
         <v>201.16157550143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.68</v>
+        <v>-2.83</v>
       </c>
       <c r="L2" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="M2" t="n">
         <v>0.34</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>3.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44601.55208333334</v>
+        <v>44602.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>200.35</v>
+        <v>201.8</v>
       </c>
       <c r="I3" t="n">
         <v>200.5094702044284</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8</v>
+        <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
         <v>2.1</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>3.82</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44610.38541666666</v>
+        <v>44610.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>198.25</v>
+        <v>195.8</v>
       </c>
       <c r="I4" t="n">
         <v>196.8091396094445</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.76</v>
+        <v>-2.97</v>
       </c>
       <c r="L4" t="n">
-        <v>1.93</v>
+        <v>3.12</v>
       </c>
       <c r="M4" t="n">
         <v>1.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.19</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>188.35</v>
+        <v>197.85</v>
       </c>
       <c r="I5" t="n">
         <v>188.9186763387197</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>-1.05</v>
       </c>
       <c r="L5" t="n">
         <v>1.43</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>10.88</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>192.8</v>
+        <v>188.5</v>
       </c>
       <c r="I6" t="n">
         <v>189.6637359697347</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.55</v>
+        <v>-4.73</v>
       </c>
       <c r="L6" t="n">
         <v>5.81</v>
       </c>
       <c r="M6" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="n">
         <v>3.55</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44659.55208333334</v>
+        <v>44662.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>185.2</v>
+        <v>186.95</v>
       </c>
       <c r="I7" t="n">
         <v>185.9092238515494</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>2.41</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>3.62</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>190.35</v>
+        <v>185.3</v>
       </c>
       <c r="I8" t="n">
         <v>185.9153960961047</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>1.82</v>
+        <v>-0.88</v>
       </c>
       <c r="L8" t="n">
         <v>1.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>5.59</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>191.95</v>
+        <v>196.55</v>
       </c>
       <c r="I9" t="n">
         <v>194.82261910829</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.59</v>
+        <v>-6.07</v>
       </c>
       <c r="L9" t="n">
-        <v>4.07</v>
+        <v>6.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.37</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>-1.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>6.11</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44694.38541666666</v>
+        <v>44694.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>194.1</v>
+        <v>189</v>
       </c>
       <c r="I10" t="n">
         <v>190.0596839233327</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.25</v>
+        <v>-3.84</v>
       </c>
       <c r="L10" t="n">
-        <v>4.63</v>
+        <v>4.66</v>
       </c>
       <c r="M10" t="n">
         <v>5.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.84</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44699.38541666666</v>
+        <v>44699.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>202.95</v>
+        <v>205.55</v>
       </c>
       <c r="I11" t="n">
         <v>203.8260442619901</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.38</v>
+        <v>-8.76</v>
       </c>
       <c r="L11" t="n">
-        <v>7.51</v>
+        <v>9.66</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>6.48</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>204.5</v>
+        <v>200.4</v>
       </c>
       <c r="I12" t="n">
         <v>201.1704780296521</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.51</v>
+        <v>-2.51</v>
       </c>
       <c r="L12" t="n">
         <v>3.55</v>
       </c>
       <c r="M12" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="N12" t="n">
         <v>2.37</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>191.5</v>
+        <v>194.9</v>
       </c>
       <c r="I13" t="n">
         <v>194.7729354801999</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>4.44</v>
+        <v>2.74</v>
       </c>
       <c r="L13" t="n">
         <v>1.6</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>201.9</v>
+        <v>196.3</v>
       </c>
       <c r="I14" t="n">
         <v>201.0860128790708</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K14" t="n">
-        <v>3.59</v>
+        <v>0.72</v>
       </c>
       <c r="L14" t="n">
         <v>2.23</v>
@@ -1239,7 +1406,7 @@
         <v>1.77</v>
       </c>
       <c r="N14" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
         <v>3.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44799.38541666666</v>
+        <v>44799.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>202.15</v>
+        <v>202.55</v>
       </c>
       <c r="I15" t="n">
         <v>202.4463893235842</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.98</v>
+        <v>-3.18</v>
       </c>
       <c r="L15" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="M15" t="n">
         <v>1.24</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>198.65</v>
+        <v>195</v>
       </c>
       <c r="I16" t="n">
         <v>195.0270367953029</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.93</v>
+        <v>-3.73</v>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>3.83</v>
       </c>
       <c r="M16" t="n">
         <v>3.24</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="O16" t="n">
         <v>1.96</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44861.55208333334</v>
+        <v>44862.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>187.15</v>
+        <v>193.2</v>
       </c>
       <c r="I17" t="n">
         <v>189.7612138051147</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>4.03</v>
+        <v>0.92</v>
       </c>
       <c r="L17" t="n">
         <v>2.51</v>
@@ -1410,7 +1613,7 @@
         <v>2.21</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="O17" t="n">
         <v>-2.67</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>5.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>196.15</v>
+        <v>190.35</v>
       </c>
       <c r="I18" t="n">
         <v>190.6714581940943</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>1.53</v>
+        <v>-1.48</v>
       </c>
       <c r="L18" t="n">
         <v>3.03</v>
       </c>
       <c r="M18" t="n">
-        <v>0.72</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="O18" t="n">
         <v>2.97</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.62</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44900.55208333334</v>
+        <v>44901.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>196.35</v>
+        <v>197.9</v>
       </c>
       <c r="I19" t="n">
         <v>197.7277022469508</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.15</v>
+        <v>-3.97</v>
       </c>
       <c r="L19" t="n">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="M19" t="n">
         <v>0.47</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>3.81</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>195.75</v>
+        <v>192.8</v>
       </c>
       <c r="I20" t="n">
         <v>193.6295176792327</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.09</v>
+        <v>-2.58</v>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>3.06</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03</v>
+        <v>0.33</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
         <v>0.97</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>4.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>197.95</v>
+        <v>200.85</v>
       </c>
       <c r="I21" t="n">
         <v>198.7890647858422</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.67</v>
+        <v>-4.18</v>
       </c>
       <c r="L21" t="n">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="N21" t="n">
         <v>1.41</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.36</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>207.45</v>
+        <v>202.55</v>
       </c>
       <c r="I22" t="n">
         <v>203.8752824419714</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>3.29</v>
+        <v>0.85</v>
       </c>
       <c r="L22" t="n">
         <v>2.27</v>
@@ -1695,7 +1958,7 @@
         <v>0.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.45</v>
+        <v>2.36</v>
       </c>
       <c r="O22" t="n">
         <v>0.35</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.88</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>202.1</v>
+        <v>206.5</v>
       </c>
       <c r="I23" t="n">
         <v>202.6541940684729</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>0.22</v>
+        <v>-1.95</v>
       </c>
       <c r="L23" t="n">
         <v>3.28</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.98</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44978.38541666666</v>
+        <v>44978.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>197.6</v>
+        <v>196.15</v>
       </c>
       <c r="I24" t="n">
         <v>197.1019321250567</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.31</v>
+        <v>-5.01</v>
       </c>
       <c r="L24" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="M24" t="n">
         <v>0.87</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44984.38541666666</v>
+        <v>44984.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>203</v>
+        <v>206.45</v>
       </c>
       <c r="I25" t="n">
         <v>205.1358206378778</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.49</v>
+        <v>-5.25</v>
       </c>
       <c r="L25" t="n">
-        <v>4.66</v>
+        <v>5.28</v>
       </c>
       <c r="M25" t="n">
         <v>0.2</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45008.55208333334</v>
+        <v>45009.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>210.65</v>
+        <v>208.3</v>
       </c>
       <c r="I26" t="n">
         <v>209.3235760335944</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>2.03</v>
+        <v>0.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.99</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.82</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>214.85</v>
+        <v>215.7</v>
       </c>
       <c r="I27" t="n">
         <v>215.489659753622</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.14</v>
+        <v>-3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="M27" t="n">
         <v>1.14</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.67</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45049.55208333334</v>
+        <v>45050.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>218.05</v>
+        <v>207.5</v>
       </c>
       <c r="I28" t="n">
         <v>212.9760836095503</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>1.09</v>
+        <v>-3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>3.2</v>
+        <v>4.17</v>
       </c>
       <c r="M28" t="n">
-        <v>0.74</v>
+        <v>2.77</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4.01</v>
       </c>
       <c r="O28" t="n">
         <v>2.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.08</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>205.8</v>
+        <v>210.25</v>
       </c>
       <c r="I29" t="n">
         <v>209.3624951967791</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>0.82</v>
+        <v>-1.33</v>
       </c>
       <c r="L29" t="n">
         <v>3.49</v>
@@ -2094,7 +2441,7 @@
         <v>0.55</v>
       </c>
       <c r="N29" t="n">
-        <v>1.76</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
         <v>-4.01</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>3.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45099.38541666666</v>
+        <v>45099.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>205.9</v>
+        <v>205.35</v>
       </c>
       <c r="I30" t="n">
         <v>205.5049360161157</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.07</v>
+        <v>-2.33</v>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
         <v>0.26</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>2.81</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45112.38541666666</v>
+        <v>45112.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>207.55</v>
+        <v>208.95</v>
       </c>
       <c r="I31" t="n">
         <v>208.0672272862681</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.07</v>
+        <v>-1.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
         <v>0.27</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.31</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>214.9</v>
+        <v>208.1</v>
       </c>
       <c r="I32" t="n">
         <v>208.5797933265183</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>2.85</v>
+        <v>-0.41</v>
       </c>
       <c r="L32" t="n">
         <v>1.82</v>
@@ -2265,7 +2648,7 @@
         <v>0.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.29</v>
+        <v>3.23</v>
       </c>
       <c r="O32" t="n">
         <v>0.97</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.86</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45146.55208333334</v>
+        <v>45147.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>207.45</v>
+        <v>215.35</v>
       </c>
       <c r="I33" t="n">
         <v>214.3241378517856</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>0.31</v>
+        <v>-3.48</v>
       </c>
       <c r="L33" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="M33" t="n">
         <v>0.48</v>
       </c>
       <c r="N33" t="n">
-        <v>0.73</v>
+        <v>3.11</v>
       </c>
       <c r="O33" t="n">
         <v>-3.23</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>5.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45155.55208333334</v>
+        <v>45156.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>206.35</v>
+        <v>202.35</v>
       </c>
       <c r="I34" t="n">
         <v>205.3627901809092</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.18</v>
+        <v>-6.04</v>
       </c>
       <c r="L34" t="n">
-        <v>5.18</v>
+        <v>6.08</v>
       </c>
       <c r="M34" t="n">
-        <v>0.09</v>
+        <v>1.67</v>
       </c>
       <c r="N34" t="n">
         <v>2.29</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.49</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45173.55208333334</v>
+        <v>45174.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>202.2</v>
+        <v>210</v>
       </c>
       <c r="I35" t="n">
         <v>204.0786550866003</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>0.07000000000000001</v>
+        <v>-3.78</v>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>4.67</v>
       </c>
       <c r="M35" t="n">
         <v>0.3</v>
       </c>
       <c r="N35" t="n">
-        <v>1.91</v>
+        <v>4.3</v>
       </c>
       <c r="O35" t="n">
         <v>-2.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.13</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>218.85</v>
+        <v>216.75</v>
       </c>
       <c r="I36" t="n">
         <v>217.9874996475397</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>4.21</v>
+        <v>3.21</v>
       </c>
       <c r="L36" t="n">
         <v>3.67</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.11</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45259.55208333334</v>
+        <v>45260.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>190.5</v>
+        <v>194.25</v>
       </c>
       <c r="I37" t="n">
         <v>191.9211593930703</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>78</v>
+        <v>78.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>12.11</v>
+        <v>10.38</v>
       </c>
       <c r="L37" t="n">
         <v>4.71</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.64</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>204.9</v>
+        <v>199.1</v>
       </c>
       <c r="I38" t="n">
         <v>199.1319856464446</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>5.48</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
         <v>2.57</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>206.85</v>
+        <v>212.3</v>
       </c>
       <c r="I39" t="n">
         <v>209.3772967173677</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.89</v>
+        <v>-6.63</v>
       </c>
       <c r="L39" t="n">
-        <v>4.34</v>
+        <v>7.26</v>
       </c>
       <c r="M39" t="n">
-        <v>0.92</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>1.46</v>
+        <v>2.63</v>
       </c>
       <c r="O39" t="n">
         <v>-3.54</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.97</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>258.15</v>
+        <v>249.1</v>
       </c>
       <c r="I40" t="n">
         <v>252.8540327850627</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K40" t="n">
-        <v>21.6</v>
+        <v>17.33</v>
       </c>
       <c r="L40" t="n">
         <v>2.05</v>
@@ -2721,7 +3200,7 @@
         <v>0.75</v>
       </c>
       <c r="N40" t="n">
-        <v>3.02</v>
+        <v>4.76</v>
       </c>
       <c r="O40" t="n">
         <v>2.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.42</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45344.55208333334</v>
+        <v>45345.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>270.9</v>
+        <v>273.5</v>
       </c>
       <c r="I41" t="n">
         <v>270.9943202997655</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.75</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>9.65</v>
+        <v>10.32</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>263.1</v>
+        <v>256.85</v>
       </c>
       <c r="I42" t="n">
         <v>259.7368043761242</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.8</v>
+        <v>-6.09</v>
       </c>
       <c r="L42" t="n">
-        <v>5.47</v>
+        <v>7.2</v>
       </c>
       <c r="M42" t="n">
         <v>0.53</v>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0.13</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>260.3</v>
+        <v>272.95</v>
       </c>
       <c r="I43" t="n">
         <v>261.5492544080782</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.34</v>
+        <v>-6.27</v>
       </c>
       <c r="L43" t="n">
-        <v>3.48</v>
+        <v>6.64</v>
       </c>
       <c r="M43" t="n">
         <v>0.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>-4.33</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>291.45</v>
+        <v>283.5</v>
       </c>
       <c r="I44" t="n">
         <v>285.6508879468868</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>6.78</v>
+        <v>3.87</v>
       </c>
       <c r="L44" t="n">
         <v>4.6</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45446.38541666666</v>
+        <v>45446.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>295.7</v>
+        <v>301.85</v>
       </c>
       <c r="I45" t="n">
         <v>295.7900829546663</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.3</v>
+        <v>-6.47</v>
       </c>
       <c r="L45" t="n">
         <v>7.9</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.13</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>301.85</v>
+        <v>266.9</v>
       </c>
       <c r="I46" t="n">
         <v>280.3287795260483</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-11.58</v>
       </c>
       <c r="L46" t="n">
-        <v>2.48</v>
+        <v>19.81</v>
       </c>
       <c r="M46" t="n">
         <v>-0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>11.71</v>
       </c>
       <c r="O46" t="n">
         <v>6.68</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>15.17</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45454.38541666666</v>
+        <v>45454.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>300.45</v>
+        <v>301.85</v>
       </c>
       <c r="I47" t="n">
         <v>301.6253947255108</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.57</v>
+        <v>-13.09</v>
       </c>
       <c r="L47" t="n">
         <v>13.45</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>325.3</v>
+        <v>318.85</v>
       </c>
       <c r="I48" t="n">
         <v>320.0297340571912</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>7.77</v>
+        <v>5.63</v>
       </c>
       <c r="L48" t="n">
         <v>2.63</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>331.95</v>
+        <v>343.35</v>
       </c>
       <c r="I49" t="n">
         <v>337.916197753859</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.11</v>
+        <v>-7.68</v>
       </c>
       <c r="L49" t="n">
-        <v>7.35</v>
+        <v>8.42</v>
       </c>
       <c r="M49" t="n">
         <v>0.95</v>
       </c>
       <c r="N49" t="n">
-        <v>3.75</v>
+        <v>5.29</v>
       </c>
       <c r="O49" t="n">
         <v>-1.64</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45537.55208333334</v>
+        <v>45538.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>348.85</v>
+        <v>345.3</v>
       </c>
       <c r="I50" t="n">
         <v>348.2043530208803</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K50" t="n">
-        <v>1.6</v>
+        <v>0.57</v>
       </c>
       <c r="L50" t="n">
         <v>4.75</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>4.56</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>320.5</v>
+        <v>325.9</v>
       </c>
       <c r="I51" t="n">
         <v>323.7206709195337</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>7.18</v>
+        <v>5.62</v>
       </c>
       <c r="L51" t="n">
         <v>2.49</v>
       </c>
       <c r="M51" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="N51" t="n">
         <v>1.64</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45588.55208333334</v>
+        <v>45589.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>329.55</v>
+        <v>322.65</v>
       </c>
       <c r="I52" t="n">
         <v>327.8153447203568</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>1.12</v>
+        <v>-1</v>
       </c>
       <c r="L52" t="n">
         <v>1.64</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.85</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>315.4</v>
+        <v>324.45</v>
       </c>
       <c r="I53" t="n">
         <v>320.2795864930574</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K53" t="n">
-        <v>2.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L53" t="n">
         <v>5.64</v>
@@ -3462,7 +4097,7 @@
         <v>1.53</v>
       </c>
       <c r="N53" t="n">
-        <v>3.34</v>
+        <v>3.71</v>
       </c>
       <c r="O53" t="n">
         <v>-1.58</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>340.25</v>
+        <v>315</v>
       </c>
       <c r="I54" t="n">
         <v>323.5173207169514</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K54" t="n">
-        <v>4.87</v>
+        <v>-2.91</v>
       </c>
       <c r="L54" t="n">
-        <v>2.62</v>
+        <v>4.52</v>
       </c>
       <c r="M54" t="n">
         <v>1.53</v>
       </c>
       <c r="N54" t="n">
-        <v>2.08</v>
+        <v>6.16</v>
       </c>
       <c r="O54" t="n">
         <v>3.71</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.06</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45708.38541666666</v>
+        <v>45708.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>295.55</v>
+        <v>299</v>
       </c>
       <c r="I55" t="n">
         <v>297.1902697555992</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>6.17</v>
+        <v>5.08</v>
       </c>
       <c r="L55" t="n">
         <v>7.24</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.81</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45716.55208333334</v>
+        <v>45719.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>276.3</v>
+        <v>275.2</v>
       </c>
       <c r="I56" t="n">
         <v>276.0188386746188</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-7.59</v>
+        <v>-7.96</v>
       </c>
       <c r="L56" t="n">
-        <v>8.68</v>
+        <v>10.8</v>
       </c>
       <c r="M56" t="n">
         <v>1.06</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>289.1</v>
+        <v>294.7</v>
       </c>
       <c r="I57" t="n">
         <v>293.0319319352194</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.05</v>
+        <v>-7.09</v>
       </c>
       <c r="L57" t="n">
-        <v>6</v>
+        <v>7.34</v>
       </c>
       <c r="M57" t="n">
         <v>0.85</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.86</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>291.05</v>
+        <v>277.1</v>
       </c>
       <c r="I58" t="n">
         <v>280.6641371696638</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.24</v>
+        <v>-5.97</v>
       </c>
       <c r="L58" t="n">
-        <v>4.56</v>
+        <v>5.97</v>
       </c>
       <c r="M58" t="n">
         <v>0.48</v>
       </c>
       <c r="N58" t="n">
-        <v>1.79</v>
+        <v>4.59</v>
       </c>
       <c r="O58" t="n">
         <v>1.71</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>286.5</v>
+        <v>288.4</v>
       </c>
       <c r="I59" t="n">
         <v>287.7132265824442</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.39</v>
+        <v>-4.08</v>
       </c>
       <c r="L59" t="n">
         <v>5.54</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.97</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>299.55</v>
+        <v>296</v>
       </c>
       <c r="I60" t="n">
         <v>298.2036405183022</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>3.87</v>
+        <v>2.64</v>
       </c>
       <c r="L60" t="n">
         <v>0.9</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.57</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45842.55208333334</v>
+        <v>45845.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>292.45</v>
+        <v>298.65</v>
       </c>
       <c r="I61" t="n">
         <v>297.3972560800135</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="L61" t="n">
         <v>3.28</v>
       </c>
       <c r="M61" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="N61" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>-0.77</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.56</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45866.55208333334</v>
+        <v>45867.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>293.9</v>
+        <v>284.7</v>
       </c>
       <c r="I62" t="n">
         <v>291.7867434681313</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.59</v>
+        <v>-4.67</v>
       </c>
       <c r="L62" t="n">
-        <v>3.28</v>
+        <v>4.94</v>
       </c>
       <c r="M62" t="n">
         <v>1.68</v>
       </c>
       <c r="N62" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="O62" t="n">
         <v>2.5</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.25</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45916.38541666666</v>
+        <v>45916.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>271.85</v>
+        <v>272.95</v>
       </c>
       <c r="I63" t="n">
         <v>272.7910175303722</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>4.51</v>
+        <v>4.13</v>
       </c>
       <c r="L63" t="n">
         <v>3.09</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>3.32</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>268.95</v>
+        <v>265.15</v>
       </c>
       <c r="I64" t="n">
         <v>265.9174559040172</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.47</v>
+        <v>-2.86</v>
       </c>
       <c r="L64" t="n">
-        <v>2.03</v>
+        <v>3.35</v>
       </c>
       <c r="M64" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="N64" t="n">
-        <v>0.92</v>
+        <v>1.77</v>
       </c>
       <c r="O64" t="n">
         <v>0.61</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>3.66</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>260.35</v>
+        <v>272.35</v>
       </c>
       <c r="I65" t="n">
         <v>269.1165345765864</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>1.81</v>
+        <v>-2.72</v>
       </c>
       <c r="L65" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="M65" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O65" t="n">
         <v>-1.77</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.18</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I66" t="n">
         <v>269.6899518513268</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.13</v>
+        <v>-1.6</v>
       </c>
       <c r="L66" t="n">
         <v>4.26</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.49</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>268.5</v>
+        <v>280.4</v>
       </c>
       <c r="I67" t="n">
         <v>275.7512072792185</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.19</v>
+        <v>-4.63</v>
       </c>
       <c r="L67" t="n">
-        <v>4.16</v>
+        <v>4.76</v>
       </c>
       <c r="M67" t="n">
         <v>1.19</v>
       </c>
       <c r="N67" t="n">
-        <v>2.5</v>
+        <v>4.66</v>
       </c>
       <c r="O67" t="n">
         <v>-1.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.19</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>271.8</v>
+        <v>270.4</v>
       </c>
       <c r="I68" t="n">
         <v>271.100522103833</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.07</v>
+        <v>-3.57</v>
       </c>
       <c r="L68" t="n">
-        <v>3.32</v>
+        <v>3.98</v>
       </c>
       <c r="M68" t="n">
         <v>0.29</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>3.76</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>272.2</v>
+        <v>274</v>
       </c>
       <c r="I69" t="n">
         <v>273.3400629935626</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.67</v>
+        <v>-1.33</v>
       </c>
       <c r="L69" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="M69" t="n">
         <v>1.12</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>3.52</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>285</v>
+        <v>278.6</v>
       </c>
       <c r="I70" t="n">
         <v>282.9222936943862</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>4.01</v>
+        <v>1.68</v>
       </c>
       <c r="L70" t="n">
         <v>0.73</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.57</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>277</v>
+        <v>289.5</v>
       </c>
       <c r="I71" t="n">
         <v>288.1166020928158</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K71" t="n">
-        <v>0.57</v>
+        <v>-3.91</v>
       </c>
       <c r="L71" t="n">
-        <v>2.73</v>
+        <v>4.81</v>
       </c>
       <c r="M71" t="n">
         <v>1.63</v>
       </c>
       <c r="N71" t="n">
-        <v>1.52</v>
+        <v>5.07</v>
       </c>
       <c r="O71" t="n">
         <v>-2.09</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.95</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46066.38541666666</v>
+        <v>46066.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>291</v>
+        <v>289.85</v>
       </c>
       <c r="I72" t="n">
         <v>290.6296273638932</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>0.52</v>
+        <v>0.12</v>
       </c>
       <c r="L72" t="n">
         <v>4.63</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,25 +5456,25 @@
         <v>5.52</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46072.55208333334</v>
+        <v>46073.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>300.7</v>
+        <v>305.9</v>
       </c>
       <c r="I73" t="n">
         <v>305.0125298378947</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.74</v>
+        <v>-5.54</v>
       </c>
       <c r="L73" t="n">
         <v>6.56</v>
       </c>
       <c r="M73" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="N73" t="n">
         <v>2.23</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.49</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>310.15</v>
+        <v>281.3</v>
       </c>
       <c r="I74" t="n">
         <v>308.562430491193</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K74" t="n">
-        <v>1.39</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>1.65</v>
+        <v>11.16</v>
       </c>
       <c r="M74" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="N74" t="n">
-        <v>3.81</v>
+        <v>9.98</v>
       </c>
       <c r="O74" t="n">
         <v>1.86</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>10.79</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>255.1</v>
+        <v>269.34</v>
       </c>
       <c r="I75" t="n">
         <v>264.8774265669312</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K75" t="n">
-        <v>9.31</v>
+        <v>4.25</v>
       </c>
       <c r="L75" t="n">
         <v>7.34</v>
       </c>
       <c r="M75" t="n">
-        <v>3.14</v>
+        <v>7.8</v>
       </c>
       <c r="N75" t="n">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="O75" t="n">
         <v>-9.98</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>271.05</v>
+        <v>266.7</v>
       </c>
       <c r="I76" t="n">
         <v>269.0623622928292</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K76" t="n">
-        <v>0.63</v>
+        <v>-0.98</v>
       </c>
       <c r="L76" t="n">
         <v>3.84</v>
@@ -4773,7 +5684,7 @@
         <v>2.66</v>
       </c>
       <c r="N76" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="O76" t="n">
         <v>5.92</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>6.4</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>272.65</v>
+        <v>282.55</v>
       </c>
       <c r="I77" t="n">
         <v>277.6059826623524</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.23</v>
+        <v>-5.94</v>
       </c>
       <c r="L77" t="n">
-        <v>4.71</v>
+        <v>6.58</v>
       </c>
       <c r="M77" t="n">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="N77" t="n">
-        <v>1.53</v>
+        <v>3.76</v>
       </c>
       <c r="O77" t="n">
         <v>-2.86</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>7.25</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>268</v>
+        <v>261.65</v>
       </c>
       <c r="I78" t="n">
         <v>265.8016412386431</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.15</v>
+        <v>-7.4</v>
       </c>
       <c r="L78" t="n">
-        <v>6.09</v>
+        <v>7.57</v>
       </c>
       <c r="M78" t="n">
         <v>0.8</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>5.65</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H79" t="n">
-        <v>266.9</v>
+        <v>274.6</v>
       </c>
       <c r="I79" t="n">
         <v>273.8309449741759</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.01</v>
+        <v>-4.95</v>
       </c>
       <c r="L79" t="n">
-        <v>2.62</v>
+        <v>5.18</v>
       </c>
       <c r="M79" t="n">
         <v>0.68</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>6.17</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46204.55208333334</v>
+        <v>46205.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>279.1</v>
+        <v>276.8</v>
       </c>
       <c r="I80" t="n">
         <v>277.289149784053</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K80" t="n">
-        <v>1.64</v>
+        <v>0.8</v>
       </c>
       <c r="L80" t="n">
         <v>2.93</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>4.55</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>280.05</v>
+        <v>280.95</v>
       </c>
       <c r="I81" t="n">
         <v>280.8555908670937</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.17</v>
+        <v>-1.5</v>
       </c>
       <c r="L81" t="n">
-        <v>2.17</v>
+        <v>2.73</v>
       </c>
       <c r="M81" t="n">
         <v>1.51</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>3.79</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>285</v>
+        <v>283.45</v>
       </c>
       <c r="I82" t="n">
         <v>283.8690740841522</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K82" t="n">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="L82" t="n">
         <v>2.83</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>4.79</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H83" t="n">
-        <v>290.35</v>
+        <v>296.05</v>
       </c>
       <c r="I83" t="n">
         <v>291.8157037556158</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.43</v>
+        <v>-4.45</v>
       </c>
       <c r="L83" t="n">
-        <v>3.72</v>
+        <v>5.08</v>
       </c>
       <c r="M83" t="n">
         <v>0.72</v>
       </c>
       <c r="N83" t="n">
-        <v>1.38</v>
+        <v>2.24</v>
       </c>
       <c r="O83" t="n">
         <v>-1.23</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>4.97</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H84" t="n">
-        <v>290.65</v>
+        <v>280.65</v>
       </c>
       <c r="I84" t="n">
         <v>284.9797373790772</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K84" t="n">
-        <v>-1.82</v>
+        <v>-5.2</v>
       </c>
       <c r="L84" t="n">
-        <v>2.72</v>
+        <v>5.64</v>
       </c>
       <c r="M84" t="n">
         <v>0.8</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,12 @@
       <c r="Q85" t="n">
         <v>6</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7391,7 +8416,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -7401,7 +8426,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -7411,7 +8436,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="8">
@@ -7421,7 +8446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -7431,7 +8456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
@@ -7441,7 +8466,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="11">
@@ -7451,7 +8476,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -7461,7 +8486,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -7471,7 +8496,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="14">
@@ -7481,7 +8506,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.15</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="15">
@@ -7491,7 +8516,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.83</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16">
@@ -7501,7 +8526,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.55</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="17">
@@ -7511,7 +8536,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.6</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="18">
@@ -7521,7 +8546,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="19">
@@ -7531,7 +8556,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.71</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
@@ -7541,7 +8566,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.22</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="21">
@@ -7551,7 +8576,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.45</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="22">
@@ -7561,7 +8586,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -7571,7 +8596,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -7581,7 +8606,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="25">
@@ -7591,7 +8616,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.06</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="26">
@@ -7601,7 +8626,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="27">
@@ -7611,7 +8636,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.14</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="28">
@@ -7621,7 +8646,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
